--- a/inst/extdata/eber_status.xlsx
+++ b/inst/extdata/eber_status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmcom-my.sharepoint.com/personal/joseph_boyd_med_uvm_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmcom-my.sharepoint.com/personal/joseph_boyd_med_uvm_edu/Documents/packages/EBVhelpR/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03C09FB-218D-4953-85B2-59DE22049607}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{51595F36-B3EB-4153-A86A-639069B8F07C}"/>
+    <workbookView xWindow="16215" yWindow="3450" windowWidth="28800" windowHeight="15345" xr2:uid="{51595F36-B3EB-4153-A86A-639069B8F07C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="102">
   <si>
     <t>EBER?</t>
   </si>
@@ -504,6 +504,24 @@
   </si>
   <si>
     <t>CTEBV-10</t>
+  </si>
+  <si>
+    <t>GM18502</t>
+  </si>
+  <si>
+    <t>GM12878</t>
+  </si>
+  <si>
+    <t>PC3Guise</t>
+  </si>
+  <si>
+    <t>SampleType</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>control</t>
   </si>
 </sst>
 </file>
@@ -552,13 +570,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -897,746 +913,1055 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FDC6E82-155C-48BE-A33F-19FD6CAE47E4}">
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="C1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="B16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="B33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="B35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="B37" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="B38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="B40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="B41" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="B42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="B43" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="B45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="B46" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="B47" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="B48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="B50" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="B51" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="B52" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+      <c r="B54" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
+      <c r="B55" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="B56" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="B58" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="B59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="B60" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+      <c r="B63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="B64" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="B66" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+      <c r="B67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+      <c r="B68" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+      <c r="B70" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="B71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+      <c r="B76" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+      <c r="B77" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="B78" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+      <c r="B79" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+      <c r="B80" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
+      <c r="B81" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>84</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+      <c r="B82" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
+      <c r="B83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>86</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+      <c r="B84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>87</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
+      <c r="B85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>88</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+      <c r="B86" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>89</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+      <c r="B87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>90</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
+      <c r="B88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>91</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
+      <c r="B89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>92</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+      <c r="B90" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>93</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+      <c r="B91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>94</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>1</v>
+      <c r="B92" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/eber_status.xlsx
+++ b/inst/extdata/eber_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmcom-my.sharepoint.com/personal/joseph_boyd_med_uvm_edu/Documents/packages/EBVhelpR/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B03C09FB-218D-4953-85B2-59DE22049607}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD906A42-A5CD-4BB1-BD41-3D1B584E3655}"/>
   <bookViews>
-    <workbookView xWindow="16215" yWindow="3450" windowWidth="28800" windowHeight="15345" xr2:uid="{51595F36-B3EB-4153-A86A-639069B8F07C}"/>
+    <workbookView xWindow="1035" yWindow="2955" windowWidth="28800" windowHeight="15345" xr2:uid="{51595F36-B3EB-4153-A86A-639069B8F07C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="103">
   <si>
     <t>EBER?</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>control</t>
+  </si>
+  <si>
+    <t>PC3Chung</t>
   </si>
 </sst>
 </file>
@@ -594,6 +597,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FDC6E82-155C-48BE-A33F-19FD6CAE47E4}">
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -1964,6 +1971,17 @@
         <v>101</v>
       </c>
     </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inst/extdata/eber_status.xlsx
+++ b/inst/extdata/eber_status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmcom-my.sharepoint.com/personal/joseph_boyd_med_uvm_edu/Documents/packages/EBVhelpR/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD906A42-A5CD-4BB1-BD41-3D1B584E3655}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6179CE7-2383-41B9-A22E-073D518E6B9C}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="2955" windowWidth="28800" windowHeight="15345" xr2:uid="{51595F36-B3EB-4153-A86A-639069B8F07C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{51595F36-B3EB-4153-A86A-639069B8F07C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="104">
   <si>
     <t>EBER?</t>
   </si>
@@ -525,6 +525,9 @@
   </si>
   <si>
     <t>PC3Chung</t>
+  </si>
+  <si>
+    <t>donor</t>
   </si>
 </sst>
 </file>
@@ -1110,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -1792,7 +1795,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -1803,7 +1806,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -1814,7 +1817,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -1825,7 +1828,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -1836,7 +1839,7 @@
         <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -1847,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -1858,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -1869,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -1880,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -1891,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -1902,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -1913,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -1924,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -1935,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">

--- a/inst/extdata/eber_status.xlsx
+++ b/inst/extdata/eber_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmcom-my.sharepoint.com/personal/joseph_boyd_med_uvm_edu/Documents/packages/EBVhelpR/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6179CE7-2383-41B9-A22E-073D518E6B9C}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{6EE9B8A9-0463-4BAD-8A36-3EE089449EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{657F32B5-CAA1-4551-ADF6-8A464871E8CC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{51595F36-B3EB-4153-A86A-639069B8F07C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="107">
   <si>
     <t>EBER?</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>D-EB-15</t>
-  </si>
-  <si>
-    <t>D-EB-16 (previously CTEBV-10)</t>
   </si>
   <si>
     <t>D-EB-62</t>
@@ -528,6 +525,18 @@
   </si>
   <si>
     <t>donor</t>
+  </si>
+  <si>
+    <t>D-EB-16</t>
+  </si>
+  <si>
+    <t>previously CTEBV-10</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>was this miscoded or what? Now D-EB-16</t>
   </si>
 </sst>
 </file>
@@ -923,13 +932,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FDC6E82-155C-48BE-A33F-19FD6CAE47E4}">
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -937,10 +946,13 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="D1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -948,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -959,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -970,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -981,10 +993,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -992,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -1003,10 +1015,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1014,10 +1026,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1025,10 +1037,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -1036,10 +1048,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -1047,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -1058,10 +1070,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -1069,10 +1081,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -1080,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1091,10 +1103,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>19</v>
       </c>
@@ -1102,887 +1114,893 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
       </c>
       <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="B32" t="s">
         <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s">
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
         <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
         <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B55" t="s">
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" t="s">
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
         <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
         <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
         <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
         <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B65" t="s">
         <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
         <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B68" t="s">
         <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
         <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
         <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
         <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B73" t="s">
         <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
         <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B86" t="s">
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
         <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" t="s">
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B96" t="s">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
